--- a/basedatos_partidas/salida/descompuestos/CT-02-01-130.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-02-01-130.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 02 Demoliciones y desmontajes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-02-01-130.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-02-01-130.xlsx
@@ -485,7 +485,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Levantado de revestimiento de piso flexible existente, ya sea vinílico en lámina o baldosa, linóleo o alfombra, incluido el adhesivo de fijación al contrapiso, ejecutado con medios manuales mediante espátula y rasqueta. Incluye la aplicación puntual de disolvente removedor en las zonas donde el adhesivo esté fuertemente adherido, el rascado hasta dejar el contrapiso limpio y sin restos que comprometan la adherencia del nuevo acabado, la ventilación del ambiente durante los trabajos, el retiro del material en sacos y la limpieza final. No incluye el bote del escombro. Medido en superficie realmente levantada.
+          <t xml:space="preserve">Levantado de revestimiento de piso flexible existente, ya sea vinílico en lámina o baldosa, linóleo o alfombra, incluido el adhesivo de fijación al afirmado, ejecutado con medios manuales mediante espátula y rasqueta. Incluye la aplicación puntual de disolvente removedor en las zonas donde el adhesivo esté fuertemente adherido, el rascado hasta dejar el afirmado limpio y sin restos que comprometan la adherencia del nuevo acabado, la ventilación del ambiente durante los trabajos, el retiro del material en sacos y la limpieza final. No incluye el bote del escombro. Medido en superficie realmente levantada.
 </t>
         </is>
       </c>
